--- a/Honda_Logi/Excel_Format/KIT60(最終加工).xlsx
+++ b/Honda_Logi/Excel_Format/KIT60(最終加工).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20B0ACC-2915-47D6-83BB-225DC9EA69B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE5F68E-9F78-425C-B61B-5DEC47DC5D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{C2790891-BF09-46E9-B683-452DD032878E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{C2790891-BF09-46E9-B683-452DD032878E}"/>
   </bookViews>
   <sheets>
     <sheet name="KIT60(最終加工)" sheetId="1" r:id="rId1"/>
@@ -386,7 +386,7 @@
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="00"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +492,14 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -516,12 +524,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -573,24 +584,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -615,14 +614,39 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -997,37 +1021,37 @@
   <dimension ref="A1:BC5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="9.125" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="9.125" style="26" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9" style="26"/>
-    <col min="10" max="11" width="9.125" style="30" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.125" style="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.125" style="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="9.125" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9" style="22"/>
+    <col min="10" max="11" width="9.125" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.125" style="22" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.125" style="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="9.125" style="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.125" style="30" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="9.125" style="26" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.125" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.125" style="26" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="9.125" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.25" style="24" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.125" style="26" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="9.125" style="22" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.125" style="24" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.125" style="26" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.125" style="28" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.125" style="25" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="9.125" style="28" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.125" style="25" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.125" style="28" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.125" style="22" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.125" style="24" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.125" style="21" bestFit="1" customWidth="1"/>
+    <col min="27" max="31" width="9.125" style="24" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.125" style="21" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="9.125" style="24" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.375" customWidth="1"/>
-    <col min="36" max="36" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="16.375" style="18" customWidth="1"/>
+    <col min="35" max="35" width="14.375" style="21" customWidth="1"/>
+    <col min="36" max="36" width="9.125" style="21" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="16.375" style="28" customWidth="1"/>
     <col min="38" max="42" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="9.125" style="28" bestFit="1" customWidth="1"/>
+    <col min="43" max="44" width="9.125" style="24" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="9" style="22"/>
-    <col min="48" max="48" width="10.25" style="22" bestFit="1" customWidth="1"/>
-    <col min="49" max="53" width="9.125" style="30" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="9.125" style="32" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="9" style="30"/>
+    <col min="48" max="48" width="10.25" style="32" bestFit="1" customWidth="1"/>
+    <col min="49" max="53" width="9.125" style="34" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="9.125" style="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:55" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -1035,9 +1059,9 @@
         <v>0</v>
       </c>
       <c r="AK1" s="3"/>
-      <c r="AT1" s="20"/>
-      <c r="AU1" s="20"/>
-      <c r="AV1" s="20"/>
+      <c r="AT1" s="18"/>
+      <c r="AU1" s="18"/>
+      <c r="AV1" s="18"/>
     </row>
     <row r="2" spans="1:55" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
@@ -1484,7 +1508,7 @@
       <c r="AX4" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="AY4" s="19" t="s">
+      <c r="AY4" s="17" t="s">
         <v>96</v>
       </c>
       <c r="AZ4" s="8" t="s">
@@ -1499,47 +1523,49 @@
       <c r="BC4" s="8"/>
     </row>
     <row r="5" spans="1:55" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.4">
-      <c r="B5" s="24"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="24"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="27"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="23"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="27"/>
-      <c r="AC5" s="27"/>
-      <c r="AD5" s="27"/>
-      <c r="AE5" s="27"/>
-      <c r="AF5" s="23"/>
-      <c r="AG5" s="27"/>
-      <c r="AK5" s="17"/>
-      <c r="AQ5" s="27"/>
-      <c r="AR5" s="27"/>
-      <c r="AT5" s="21"/>
-      <c r="AU5" s="21"/>
-      <c r="AV5" s="21"/>
-      <c r="AW5" s="29"/>
-      <c r="AX5" s="29"/>
-      <c r="AY5" s="29"/>
-      <c r="AZ5" s="29"/>
-      <c r="BA5" s="29"/>
-      <c r="BB5" s="31"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="20"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="23"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="19"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23"/>
+      <c r="AC5" s="23"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="23"/>
+      <c r="AF5" s="19"/>
+      <c r="AG5" s="23"/>
+      <c r="AI5" s="19"/>
+      <c r="AJ5" s="19"/>
+      <c r="AK5" s="27"/>
+      <c r="AQ5" s="23"/>
+      <c r="AR5" s="23"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="31"/>
+      <c r="AW5" s="33"/>
+      <c r="AX5" s="33"/>
+      <c r="AY5" s="33"/>
+      <c r="AZ5" s="33"/>
+      <c r="BA5" s="33"/>
+      <c r="BB5" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
